--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D4ED88-E518-4ACC-87FC-2CC94DF03511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA16893F-8966-4339-BAC3-0104C590A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>Company Wise</t>
   </si>
@@ -318,14 +318,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -607,9 +607,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C2B0EE-D568-4947-BF62-11F4617CA033}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -650,7 +671,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -661,7 +682,7 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="11"/>
       <c r="E5" t="s">
         <v>19</v>
       </c>
@@ -670,7 +691,7 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="11"/>
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -679,21 +700,21 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="11"/>
       <c r="E7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -704,7 +725,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="9"/>
+      <c r="C10" s="11"/>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
@@ -713,7 +734,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="9"/>
+      <c r="C11" s="11"/>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
@@ -722,7 +743,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="9"/>
+      <c r="C12" s="11"/>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
@@ -731,7 +752,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="9"/>
+      <c r="C13" s="11"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -740,12 +761,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
@@ -759,12 +780,12 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
@@ -831,12 +852,12 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA16893F-8966-4339-BAC3-0104C590A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
     <sheet name="PrefixSum" sheetId="1" r:id="rId2"/>
-    <sheet name="Source" sheetId="3" r:id="rId3"/>
+    <sheet name="Sliding Window" sheetId="4" r:id="rId3"/>
+    <sheet name="Source" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>Company Wise</t>
   </si>
@@ -885,6 +886,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8712B1-F73E-45FE-B8C3-C6E240F961E5}">
+  <dimension ref="A2:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A4341A-8970-49E7-87F8-7C27F48C50D8}">
   <dimension ref="A2:B17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{552A5B23-496A-45C7-9085-3344CCC24443}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>Company Wise</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/range-sum-query-immutable/description/</t>
+  </si>
+  <si>
+    <t>More prbms</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DQMxp7TS2BI?list=PLQ7ZAf76c0ZPAnTKbEMAvGYaQWBvpLCf7</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FMdN_OCfOI0iAeDlqswCiC2DZzD4nPsb/view</t>
   </si>
 </sst>
 </file>
@@ -343,6 +352,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -887,7 +900,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8712B1-F73E-45FE-B8C3-C6E240F961E5}">
-  <dimension ref="A2:F2"/>
+  <dimension ref="A2:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -908,6 +921,14 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -972,6 +993,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>2</v>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{552A5B23-496A-45C7-9085-3344CCC24443}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46F63155-8F15-436D-965D-16DA6C3E966C}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -927,11 +927,14 @@
       <c r="A12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{0F700B46-E237-47B7-82CB-C993662E03E7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46F63155-8F15-436D-965D-16DA6C3E966C}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{798173FF-3008-48FF-B506-75F86104B221}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="93">
   <si>
     <t>Company Wise</t>
   </si>
@@ -193,13 +193,170 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1FMdN_OCfOI0iAeDlqswCiC2DZzD4nPsb/view</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Max Consective Ones III</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minimum Window Substring</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1B5E20"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Permutation in String</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1B5E20"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Find All Anagrams in a String</t>
+    </r>
+  </si>
+  <si>
+    <t>Maximum Average Subarray</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Find All Anagrams in a String</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Longest Substring with K Uniques</t>
+  </si>
+  <si>
+    <t>Permutation in String</t>
+  </si>
+  <si>
+    <t>Minimum Window Substring</t>
+  </si>
+  <si>
+    <t>Substring with Concatenation of All Words</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>Maximum Sum Subarray of Size K</t>
+  </si>
+  <si>
+    <t>Max Consecutive ones</t>
+  </si>
+  <si>
+    <t>Max Consecutive ones III</t>
+  </si>
+  <si>
+    <t>Subarray Product Less Than K</t>
+  </si>
+  <si>
+    <t>Fruits Into Baskets</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+  </si>
+  <si>
+    <t>Subarray with k distinct integers</t>
+  </si>
+  <si>
+    <t>Sliding Window - Fixed Size</t>
+  </si>
+  <si>
+    <t>Maximum Average Subarray I</t>
+  </si>
+  <si>
+    <t>Maximum Number of Vowels in a Substring of Given Length</t>
+  </si>
+  <si>
+    <t>Maximum Sum of Distinct Subarrays With Length K</t>
+  </si>
+  <si>
+    <t>Sliding Window - Dynamic Size</t>
+  </si>
+  <si>
+    <t>Longest Repeating Character Replacement</t>
+  </si>
+  <si>
+    <t>Max Consecutive Ones III</t>
+  </si>
+  <si>
+    <t>Count Number of Nice Subarrays</t>
+  </si>
+  <si>
+    <t>Fruit Into Baskets</t>
+  </si>
+  <si>
+    <t>Maximum Points You Can Obtain from Cards</t>
+  </si>
+  <si>
+    <t>Frequency of the Most Frequent Element</t>
+  </si>
+  <si>
+    <t>Longest Substring with At Most K Distinct Char</t>
+  </si>
+  <si>
+    <t>Longest Substring with At Least K Repeating Characters</t>
+  </si>
+  <si>
+    <t>Minimum Window Subsequence</t>
+  </si>
+  <si>
+    <t>Subarrays with K Different Integers</t>
+  </si>
+  <si>
+    <t>Max Sum Subarray of Size K</t>
+  </si>
+  <si>
+    <t>First negative number in every window of size K</t>
+  </si>
+  <si>
+    <t>Chocolate Distribution Problem</t>
+  </si>
+  <si>
+    <t>Smallest subarray with sum greater than x </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +405,30 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1B5E20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -313,7 +494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -330,12 +511,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -685,7 +880,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -696,7 +891,7 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
+      <c r="C5" s="12"/>
       <c r="E5" t="s">
         <v>19</v>
       </c>
@@ -705,7 +900,7 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="12"/>
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -714,7 +909,7 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="12"/>
       <c r="E7" t="s">
         <v>21</v>
       </c>
@@ -728,7 +923,7 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -739,7 +934,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="11"/>
+      <c r="C10" s="12"/>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
@@ -748,7 +943,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="11"/>
+      <c r="C11" s="12"/>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
@@ -757,7 +952,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="11"/>
+      <c r="C12" s="12"/>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
@@ -766,7 +961,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="11"/>
+      <c r="C13" s="12"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -900,8 +1095,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8712B1-F73E-45FE-B8C3-C6E240F961E5}">
-  <dimension ref="A2:F12"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A2:J63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="32.6328125" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -923,17 +1125,368 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C4" s="12"/>
+      <c r="E4" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C5" s="12"/>
+      <c r="E5" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C6" s="12"/>
+      <c r="E6" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C7" s="12"/>
+      <c r="E7" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="12"/>
+      <c r="E8" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C9" s="12"/>
+      <c r="E9" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C10" s="12"/>
+      <c r="E10" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C11" s="12"/>
+      <c r="E11" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="C12" s="12"/>
+      <c r="E12" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C15" s="12"/>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C16" s="12"/>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C17" s="12"/>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C18" s="12"/>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C19" s="12"/>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C20" s="12"/>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C21" s="12"/>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C22" s="12"/>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C23" s="12"/>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C24" s="12"/>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C25" s="12"/>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C26" s="12"/>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C27" s="12"/>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C28" s="12"/>
+      <c r="E28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C29" s="12"/>
+      <c r="E29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C31" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C32" s="12"/>
+      <c r="E32" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" s="12"/>
+      <c r="E33" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C34" s="12"/>
+      <c r="E34" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C35" s="12"/>
+      <c r="E35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C36" s="12"/>
+      <c r="E36" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C37" s="12"/>
+      <c r="E37" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" s="12"/>
+      <c r="E38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" s="12"/>
+      <c r="E39" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" s="12"/>
+      <c r="E40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" s="12"/>
+      <c r="E41" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" s="12"/>
+      <c r="E42" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" s="12"/>
+      <c r="E43" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C44" s="12"/>
+      <c r="E44" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C45" s="12"/>
+      <c r="E45" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C46" s="12"/>
+      <c r="E46" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C47" s="12"/>
+      <c r="E47" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C48" s="12"/>
+      <c r="E48" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C49" s="12"/>
+      <c r="E49" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C50" s="12"/>
+      <c r="E50" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C51" s="12"/>
+      <c r="E51" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C52" s="12"/>
+      <c r="E52" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:C12"/>
+    <mergeCell ref="C14:C29"/>
+    <mergeCell ref="C31:C52"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{0F700B46-E237-47B7-82CB-C993662E03E7}"/>
+    <hyperlink ref="B63" r:id="rId1" xr:uid="{0F700B46-E237-47B7-82CB-C993662E03E7}"/>
+    <hyperlink ref="E32" r:id="rId2" display="https://algomaster.io/practice/dsa/maximum-average-subarray-i?list=am-600" xr:uid="{4B6ABDC2-5F5B-45F9-8D36-410DEC5C71F8}"/>
+    <hyperlink ref="E33" r:id="rId3" display="https://algomaster.io/practice/dsa/find-all-anagrams-in-a-string?list=am-600" xr:uid="{365FA2CA-084B-4E69-A28D-203D7DF848A0}"/>
+    <hyperlink ref="E34" r:id="rId4" display="https://algomaster.io/practice/dsa/permutation-in-string?list=am-600" xr:uid="{76967222-C11D-4660-B96A-51301E09DE35}"/>
+    <hyperlink ref="E35" r:id="rId5" display="https://algomaster.io/practice/dsa/maximum-number-of-vowels-in-a-substring-of-given-length?list=am-600" xr:uid="{536E7C57-A3B6-4CE8-A0B2-B7877C31B1F9}"/>
+    <hyperlink ref="E36" r:id="rId6" display="https://algomaster.io/practice/dsa/maximum-sum-of-distinct-subarrays-with-length-k?list=am-600" xr:uid="{0E31D541-E4EE-4749-BAC3-4FDF27D0CAE7}"/>
+    <hyperlink ref="E37" r:id="rId7" display="https://algomaster.io/practice/dsa/substring-with-concatenation-of-all-words?list=am-600" xr:uid="{6CA3D75A-0FBD-4876-908F-21225B173257}"/>
+    <hyperlink ref="E39" r:id="rId8" display="https://algomaster.io/practice/dsa/longest-substring-without-repeating-characters?list=am-600" xr:uid="{987BC6C2-5BE3-424B-96F8-07832587DB28}"/>
+    <hyperlink ref="E40" r:id="rId9" display="https://algomaster.io/practice/dsa/longest-repeating-character-replacement?list=am-600" xr:uid="{881A9CD1-29D3-40AB-BC11-0DB599654C32}"/>
+    <hyperlink ref="E41" r:id="rId10" display="https://algomaster.io/practice/dsa/minimum-size-subarray-sum?list=am-600" xr:uid="{6F26E151-0ED4-4290-80C4-5D5AB8A3DB3F}"/>
+    <hyperlink ref="E42" r:id="rId11" display="https://algomaster.io/practice/dsa/max-consecutive-ones-iii?list=am-600" xr:uid="{B1A2B2B1-CAC8-409C-85DE-4E5516F633C2}"/>
+    <hyperlink ref="E43" r:id="rId12" display="https://algomaster.io/practice/dsa/count-number-of-nice-subarrays?list=am-600" xr:uid="{07BB4755-5C3F-4DA1-98A6-132372E37D97}"/>
+    <hyperlink ref="E44" r:id="rId13" display="https://algomaster.io/practice/dsa/fruit-into-baskets?list=am-600" xr:uid="{258B347F-C6B2-49EF-8665-6A2992C64A26}"/>
+    <hyperlink ref="E45" r:id="rId14" display="https://algomaster.io/practice/dsa/maximum-points-you-can-obtain-from-cards?list=am-600" xr:uid="{7363D5BF-D1D2-421E-8DA8-F7F2DC62D4DF}"/>
+    <hyperlink ref="E46" r:id="rId15" display="https://algomaster.io/practice/dsa/subarray-product-less-than-k?list=am-600" xr:uid="{2B20628E-7F6E-4564-B90C-DB3C8441B2B2}"/>
+    <hyperlink ref="E47" r:id="rId16" display="https://algomaster.io/practice/dsa/frequency-of-the-most-frequent-element?list=am-600" xr:uid="{F2C9F58F-11D1-4E26-B108-8D9B97BE6372}"/>
+    <hyperlink ref="E48" r:id="rId17" display="https://algomaster.io/practice/dsa/longest-substring-with-at-most-k-distinct-characters?list=am-600" xr:uid="{ABFEEC13-0E8E-4611-8880-3776F9075A2E}"/>
+    <hyperlink ref="E49" r:id="rId18" display="https://algomaster.io/practice/dsa/longest-substring-with-at-least-k-repeating-characters?list=am-600" xr:uid="{666FB53B-D203-4949-B8A6-3AD32693B258}"/>
+    <hyperlink ref="E50" r:id="rId19" display="https://algomaster.io/practice/dsa/minimum-window-substring?list=am-600" xr:uid="{DD368B40-ED78-486C-9449-65CD6297DA6A}"/>
+    <hyperlink ref="E51" r:id="rId20" display="https://algomaster.io/practice/dsa/minimum-window-subsequence?list=am-600" xr:uid="{98AD112B-3412-4A8D-9079-72C7B1E5E9FD}"/>
+    <hyperlink ref="E52" r:id="rId21" display="https://algomaster.io/practice/dsa/subarrays-with-k-different-integers?list=am-600" xr:uid="{12F69754-C1B2-461D-8A0F-CDD9CA6A52A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{66FF51C3-91AD-4BAC-AD08-15859D595155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{798173FF-3008-48FF-B506-75F86104B221}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B44F8F-546A-4221-94F8-68CCF13E2CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
     <sheet name="PrefixSum" sheetId="1" r:id="rId2"/>
     <sheet name="Sliding Window" sheetId="4" r:id="rId3"/>
-    <sheet name="Source" sheetId="3" r:id="rId4"/>
+    <sheet name="LinkedList" sheetId="5" r:id="rId4"/>
+    <sheet name="Stack" sheetId="6" r:id="rId5"/>
+    <sheet name="Source" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>Company Wise</t>
   </si>
@@ -356,7 +358,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,6 +431,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -514,23 +524,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -547,10 +557,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -880,7 +886,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -891,7 +897,7 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="17"/>
       <c r="E5" t="s">
         <v>19</v>
       </c>
@@ -900,7 +906,7 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="17"/>
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -909,7 +915,7 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="17"/>
       <c r="E7" t="s">
         <v>21</v>
       </c>
@@ -923,7 +929,7 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="17" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -934,7 +940,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="12"/>
+      <c r="C10" s="17"/>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
@@ -943,7 +949,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="12"/>
+      <c r="C11" s="17"/>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
@@ -952,7 +958,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="12"/>
+      <c r="C12" s="17"/>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
@@ -961,7 +967,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="12"/>
+      <c r="C13" s="17"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -1126,64 +1132,64 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C4" s="12"/>
-      <c r="E4" s="15" t="s">
+      <c r="C4" s="17"/>
+      <c r="E4" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="12"/>
-      <c r="E5" s="14" t="s">
+      <c r="C5" s="17"/>
+      <c r="E5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="C6" s="17"/>
+      <c r="E6" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="12"/>
-      <c r="E7" s="13" t="s">
+      <c r="C7" s="17"/>
+      <c r="E7" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C8" s="12"/>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="17"/>
+      <c r="E8" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="12"/>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="17"/>
+      <c r="E9" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="12"/>
-      <c r="E10" s="13" t="s">
+      <c r="C10" s="17"/>
+      <c r="E10" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="12"/>
-      <c r="E11" s="16" t="s">
+      <c r="C11" s="17"/>
+      <c r="E11" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="12"/>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="17"/>
+      <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1196,99 +1202,99 @@
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C15" s="12"/>
+      <c r="C15" s="17"/>
       <c r="E15" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C16" s="12"/>
+      <c r="C16" s="17"/>
       <c r="E16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="12"/>
+      <c r="C17" s="17"/>
       <c r="E17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C18" s="12"/>
+      <c r="C18" s="17"/>
       <c r="E18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C19" s="12"/>
+      <c r="C19" s="17"/>
       <c r="E19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C20" s="12"/>
+      <c r="C20" s="17"/>
       <c r="E20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C21" s="12"/>
-      <c r="E21" t="s">
+      <c r="C21" s="17"/>
+      <c r="E21" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C22" s="12"/>
+      <c r="C22" s="17"/>
       <c r="E22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C23" s="12"/>
+      <c r="C23" s="17"/>
       <c r="E23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C24" s="12"/>
+      <c r="C24" s="17"/>
       <c r="E24" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C25" s="12"/>
+      <c r="C25" s="17"/>
       <c r="E25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C26" s="12"/>
+      <c r="C26" s="17"/>
       <c r="E26" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C27" s="12"/>
+      <c r="C27" s="17"/>
       <c r="E27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C28" s="12"/>
+      <c r="C28" s="17"/>
       <c r="E28" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C29" s="12"/>
+      <c r="C29" s="17"/>
       <c r="E29" t="s">
         <v>73</v>
       </c>
@@ -1306,135 +1312,135 @@
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C32" s="12"/>
+      <c r="C32" s="17"/>
       <c r="E32" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="12"/>
+      <c r="C33" s="17"/>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="12"/>
+      <c r="C34" s="17"/>
       <c r="E34" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="12"/>
+      <c r="C35" s="17"/>
       <c r="E35" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="12"/>
+      <c r="C36" s="17"/>
       <c r="E36" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="12"/>
+      <c r="C37" s="17"/>
       <c r="E37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="12"/>
+      <c r="C38" s="17"/>
       <c r="E38" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="12"/>
+      <c r="C39" s="17"/>
       <c r="E39" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="12"/>
+      <c r="C40" s="17"/>
       <c r="E40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="12"/>
+      <c r="C41" s="17"/>
       <c r="E41" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="12"/>
+      <c r="C42" s="17"/>
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="12"/>
+      <c r="C43" s="17"/>
       <c r="E43" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="12"/>
+      <c r="C44" s="17"/>
       <c r="E44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="12"/>
+      <c r="C45" s="17"/>
       <c r="E45" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="12"/>
+      <c r="C46" s="17"/>
       <c r="E46" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="12"/>
+      <c r="C47" s="17"/>
       <c r="E47" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="12"/>
+      <c r="C48" s="17"/>
       <c r="E48" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C49" s="12"/>
+      <c r="C49" s="17"/>
       <c r="E49" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C50" s="12"/>
+      <c r="C50" s="17"/>
       <c r="E50" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C51" s="12"/>
+      <c r="C51" s="17"/>
       <c r="E51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C52" s="12"/>
+      <c r="C52" s="17"/>
       <c r="E52" s="1" t="s">
         <v>88</v>
       </c>
@@ -1493,6 +1499,66 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7C268B-0F05-4BDD-888C-4499121F892A}">
+  <dimension ref="A2:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAEF6E5-7B71-4679-AA65-7B980562DC80}">
+  <dimension ref="A2:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A4341A-8970-49E7-87F8-7C27F48C50D8}">
   <dimension ref="A2:B17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B44F8F-546A-4221-94F8-68CCF13E2CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CDB0AB-1BCC-465D-8B08-CA5184B7DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2750" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="157">
   <si>
     <t>Company Wise</t>
   </si>
@@ -352,6 +352,198 @@
   </si>
   <si>
     <t>Smallest subarray with sum greater than x </t>
+  </si>
+  <si>
+    <t>Reverse Linked List</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted Lists</t>
+  </si>
+  <si>
+    <t>Remove Nth Node from End</t>
+  </si>
+  <si>
+    <t>Add Two Numbers</t>
+  </si>
+  <si>
+    <t>Copy List with Random Pointer</t>
+  </si>
+  <si>
+    <t>Swap Nodes in Pairs</t>
+  </si>
+  <si>
+    <t>Rotate Lis</t>
+  </si>
+  <si>
+    <t>Basic Operations</t>
+  </si>
+  <si>
+    <t>Search in Linked List</t>
+  </si>
+  <si>
+    <t>Insert at Head / Tail / Nth Position</t>
+  </si>
+  <si>
+    <t>Delete Head / Tail / Nth Node</t>
+  </si>
+  <si>
+    <t>Intersection of Two Linked Lists</t>
+  </si>
+  <si>
+    <t>Design Linked List</t>
+  </si>
+  <si>
+    <t>Odd–Even Linked List</t>
+  </si>
+  <si>
+    <t>Fast and Slow Pointer</t>
+  </si>
+  <si>
+    <t>Middle of the Linked List</t>
+  </si>
+  <si>
+    <t>Linked List Cycle</t>
+  </si>
+  <si>
+    <t>Linked List Cycle II</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End</t>
+  </si>
+  <si>
+    <t>Reversal Pattern</t>
+  </si>
+  <si>
+    <t>Reverse a Linked List</t>
+  </si>
+  <si>
+    <t>Palindrome Linked List</t>
+  </si>
+  <si>
+    <t>Reverse Linked List II (between m &amp; n)</t>
+  </si>
+  <si>
+    <t>Maximum Twin Sum of a Linked List</t>
+  </si>
+  <si>
+    <t>Rotate List (circular linkedlist)</t>
+  </si>
+  <si>
+    <t>Reverse Nodes in k-Group</t>
+  </si>
+  <si>
+    <t>Merge/Sort</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from Sorted List</t>
+  </si>
+  <si>
+    <t>Sort List</t>
+  </si>
+  <si>
+    <t>Reorder List</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from Sorted List II</t>
+  </si>
+  <si>
+    <t>Partition List</t>
+  </si>
+  <si>
+    <t>Merge K Sorted Lists</t>
+  </si>
+  <si>
+    <t>LinkedList With Stack/HashMap</t>
+  </si>
+  <si>
+    <t>Add Two Numbers II</t>
+  </si>
+  <si>
+    <t>Next Greater Node in Linked List</t>
+  </si>
+  <si>
+    <t>Remove Nodes From Linked List</t>
+  </si>
+  <si>
+    <t>Doublr Linked List</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Implement Doubly Linked List</t>
+  </si>
+  <si>
+    <t>Insert a node in a doubly Linkedlist</t>
+  </si>
+  <si>
+    <t>Delete a node from a doubly Linkedlist</t>
+  </si>
+  <si>
+    <t>Reverse Doubly Linked List</t>
+  </si>
+  <si>
+    <t>LRU Cache</t>
+  </si>
+  <si>
+    <t>LFU Cache</t>
+  </si>
+  <si>
+    <t>Merge/Sort/Reorder</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted DLLs</t>
+  </si>
+  <si>
+    <t>Flatten Multilevel DLL</t>
+  </si>
+  <si>
+    <t>Convert DLL to Binary Tree</t>
+  </si>
+  <si>
+    <t>Design Linked Lis</t>
+  </si>
+  <si>
+    <t>Delete the Middle Node of a Linked List</t>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List</t>
+  </si>
+  <si>
+    <t>Odd Even Linked List</t>
+  </si>
+  <si>
+    <t>Partition Lis</t>
+  </si>
+  <si>
+    <t>Rotate List</t>
+  </si>
+  <si>
+    <t>Delete Node in a Linked List</t>
+  </si>
+  <si>
+    <t>Flatten a Multilevel Doubly Linked List</t>
+  </si>
+  <si>
+    <t>Insert into a Sorted Circular Linked List</t>
+  </si>
+  <si>
+    <t>Merge In Between Linked Lists</t>
+  </si>
+  <si>
+    <t>LinkedList In-place Reversal</t>
+  </si>
+  <si>
+    <t>Reverse Linked List II</t>
+  </si>
+  <si>
+    <t>Fast and Slow Pointers</t>
+  </si>
+  <si>
+    <t>Happy Number</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
 </sst>
 </file>
@@ -504,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -535,6 +727,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -886,7 +1081,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -897,7 +1092,7 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
+      <c r="C5" s="18"/>
       <c r="E5" t="s">
         <v>19</v>
       </c>
@@ -906,7 +1101,7 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -915,7 +1110,7 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
       <c r="E7" t="s">
         <v>21</v>
       </c>
@@ -929,7 +1124,7 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -940,7 +1135,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="17"/>
+      <c r="C10" s="18"/>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
@@ -949,7 +1144,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="17"/>
+      <c r="C11" s="18"/>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
@@ -958,7 +1153,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="17"/>
+      <c r="C12" s="18"/>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
@@ -967,7 +1162,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="17"/>
+      <c r="C13" s="18"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -1132,63 +1327,87 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
       </c>
       <c r="E3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" t="s">
+        <v>156</v>
+      </c>
       <c r="E4" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="17"/>
+      <c r="C5" s="18"/>
       <c r="E5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
       <c r="E6" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" t="s">
+        <v>156</v>
+      </c>
       <c r="E7" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" t="s">
+        <v>156</v>
+      </c>
       <c r="E8" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" t="s">
+        <v>156</v>
+      </c>
       <c r="E9" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
       <c r="E10" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
       <c r="E11" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" t="s">
+        <v>156</v>
+      </c>
       <c r="E12" s="14" t="s">
         <v>57</v>
       </c>
@@ -1202,7 +1421,7 @@
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="15" t="s">
@@ -1210,91 +1429,100 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C15" s="17"/>
+      <c r="C15" s="18"/>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
       <c r="E15" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" t="s">
+        <v>156</v>
+      </c>
       <c r="E16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="17"/>
+      <c r="C17" s="18"/>
       <c r="E17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C18" s="17"/>
+      <c r="C18" s="18"/>
       <c r="E18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C19" s="17"/>
+      <c r="C19" s="18"/>
       <c r="E19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C20" s="17"/>
+      <c r="C20" s="18"/>
       <c r="E20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C21" s="17"/>
+      <c r="C21" s="18"/>
       <c r="E21" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C22" s="17"/>
+      <c r="C22" s="18"/>
       <c r="E22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="E23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" t="s">
+        <v>156</v>
+      </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C25" s="17"/>
+      <c r="C25" s="18"/>
       <c r="E25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C26" s="17"/>
+      <c r="C26" s="18"/>
       <c r="E26" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C27" s="17"/>
+      <c r="C27" s="18"/>
       <c r="E27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C28" s="17"/>
+      <c r="C28" s="18"/>
       <c r="E28" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C29" s="17"/>
+      <c r="C29" s="18"/>
       <c r="E29" t="s">
         <v>73</v>
       </c>
@@ -1312,7 +1540,7 @@
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="15" t="s">
@@ -1320,127 +1548,139 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" t="s">
+        <v>156</v>
+      </c>
       <c r="E32" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" t="s">
+        <v>156</v>
+      </c>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="17"/>
+      <c r="C34" s="18"/>
       <c r="E34" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="17"/>
+      <c r="C35" s="18"/>
       <c r="E35" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="17"/>
+      <c r="C36" s="18"/>
       <c r="E36" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="17"/>
+      <c r="C37" s="18"/>
       <c r="E37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="17"/>
-      <c r="E38" t="s">
+      <c r="C38" s="18"/>
+      <c r="E38" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" t="s">
+        <v>156</v>
+      </c>
       <c r="E39" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="17"/>
+      <c r="C40" s="18"/>
       <c r="E40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="17"/>
+      <c r="C41" s="18"/>
       <c r="E41" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" t="s">
+        <v>156</v>
+      </c>
       <c r="E42" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="17"/>
+      <c r="C43" s="18"/>
       <c r="E43" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="17"/>
+      <c r="C44" s="18"/>
       <c r="E44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="17"/>
+      <c r="C45" s="18"/>
       <c r="E45" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="17"/>
+      <c r="C46" s="18"/>
       <c r="E46" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="17"/>
+      <c r="C47" s="18"/>
       <c r="E47" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="17"/>
+      <c r="C48" s="18"/>
       <c r="E48" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C49" s="17"/>
+      <c r="C49" s="18"/>
       <c r="E49" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C50" s="17"/>
+      <c r="C50" s="18"/>
       <c r="E50" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C51" s="17"/>
+      <c r="C51" s="18"/>
       <c r="E51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C52" s="17"/>
+      <c r="C52" s="18"/>
       <c r="E52" s="1" t="s">
         <v>88</v>
       </c>
@@ -1495,15 +1735,21 @@
     <hyperlink ref="E52" r:id="rId21" display="https://algomaster.io/practice/dsa/subarrays-with-k-different-integers?list=am-600" xr:uid="{12F69754-C1B2-461D-8A0F-CDD9CA6A52A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7C268B-0F05-4BDD-888C-4499121F892A}">
-  <dimension ref="A2:F2"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A2:G84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="9.36328125" customWidth="1"/>
+    <col min="5" max="5" width="33.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1523,7 +1769,542 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C4" s="18"/>
+      <c r="E4" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C5" s="18"/>
+      <c r="E5" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C6" s="18"/>
+      <c r="E6" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C7" s="18"/>
+      <c r="E7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C8" s="18"/>
+      <c r="E8" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C9" s="18"/>
+      <c r="E9" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C11" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C12" s="18"/>
+      <c r="E12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C13" s="18"/>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C14" s="18"/>
+      <c r="E14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C15" s="18"/>
+      <c r="E15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C16" s="18"/>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C17" s="18"/>
+      <c r="E17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C18" s="18"/>
+      <c r="E18" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C19" s="18"/>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C20" s="18"/>
+      <c r="E20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C21" s="18"/>
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C22" s="18"/>
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C23" s="18"/>
+      <c r="E23" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C24" s="18"/>
+      <c r="E24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C25" s="18"/>
+      <c r="E25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C26" s="18"/>
+      <c r="E26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C27" s="18"/>
+      <c r="E27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C28" s="18"/>
+      <c r="E28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C29" s="18"/>
+      <c r="E29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C30" s="18"/>
+      <c r="E30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C31" s="18"/>
+      <c r="E31" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C32" s="18"/>
+      <c r="E32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" s="18"/>
+      <c r="E33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C34" s="18"/>
+      <c r="E34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C35" s="18"/>
+      <c r="E35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C36" s="18"/>
+      <c r="E36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C37" s="18"/>
+      <c r="E37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" s="18"/>
+      <c r="E38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" s="18"/>
+      <c r="E39" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" s="18"/>
+      <c r="E40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" s="18"/>
+      <c r="E41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" s="18"/>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" s="18"/>
+      <c r="E43" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C44" s="18"/>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C45" s="18"/>
+      <c r="E45" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C46" s="18"/>
+      <c r="E46" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C47" s="18"/>
+      <c r="E47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C48" s="18"/>
+      <c r="E48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C49" s="18"/>
+      <c r="E49" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C50" s="18"/>
+      <c r="E50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C51" s="18"/>
+      <c r="E51" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C52" s="18"/>
+      <c r="E52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C53" s="18"/>
+      <c r="E53" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C54" s="18"/>
+      <c r="E54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C55" s="18"/>
+      <c r="E55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C56" s="18"/>
+      <c r="E56" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C58" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C59" s="18"/>
+      <c r="E59" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C60" s="18"/>
+      <c r="E60" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C61" s="18"/>
+      <c r="E61" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C62" s="18"/>
+      <c r="E62" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C63" s="18"/>
+      <c r="E63" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C64" s="18"/>
+      <c r="E64" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="18"/>
+      <c r="E65" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="18"/>
+      <c r="E66" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C67" s="18"/>
+      <c r="E67" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C68" s="18"/>
+      <c r="E68" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C69" s="18"/>
+      <c r="E69" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C70" s="18"/>
+      <c r="E70" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C71" s="18"/>
+      <c r="E71" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C72" s="18"/>
+      <c r="E72" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C73" s="18"/>
+      <c r="E73" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C74" s="18"/>
+      <c r="E74" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C75" s="18"/>
+      <c r="E75" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C76" s="18"/>
+      <c r="E76" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C77" s="18"/>
+      <c r="E77" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C78" s="18"/>
+      <c r="E78" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C79" s="18"/>
+      <c r="E79" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C80" s="18"/>
+      <c r="E80" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C81" s="18"/>
+      <c r="E81" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C82" s="18"/>
+      <c r="E82" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C83" s="18"/>
+      <c r="E83" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C84" s="18"/>
+      <c r="E84" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="C11:C56"/>
+    <mergeCell ref="C58:C84"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E58" r:id="rId1" display="https://algomaster.io/practice/dsa/intersection-of-two-linked-lists?list=am-600" xr:uid="{804095C8-0F1F-431B-AFFA-9049A574F9C2}"/>
+    <hyperlink ref="E59" r:id="rId2" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list?list=am-600" xr:uid="{22500AE3-3119-4C8A-B101-B6EF3E5F28F7}"/>
+    <hyperlink ref="E60" r:id="rId3" display="https://algomaster.io/practice/dsa/design-linked-list?list=am-600" xr:uid="{0A27B262-F4FB-4CA5-AF8B-FCED30D27874}"/>
+    <hyperlink ref="E61" r:id="rId4" display="https://algomaster.io/practice/dsa/delete-the-middle-node-of-a-linked-list?list=am-600" xr:uid="{487BFEA0-A6C3-4865-984D-84FF2576F3B7}"/>
+    <hyperlink ref="E62" r:id="rId5" display="https://algomaster.io/practice/dsa/remove-nth-node-from-end-of-list?list=am-600" xr:uid="{44428435-57A0-4B31-A499-462B0FE3B5AA}"/>
+    <hyperlink ref="E63" r:id="rId6" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list-ii?list=am-600" xr:uid="{0F5F3F7B-28F8-4DDA-ACD5-EC0BF47970D1}"/>
+    <hyperlink ref="E64" r:id="rId7" display="https://algomaster.io/practice/dsa/odd-even-linked-list?list=am-600" xr:uid="{FC921715-4514-4657-822C-6E1E6B015430}"/>
+    <hyperlink ref="E65" r:id="rId8" display="https://algomaster.io/practice/dsa/swap-nodes-in-pairs?list=am-600" xr:uid="{1C2D3151-2C70-432E-81FB-9EAC732DF921}"/>
+    <hyperlink ref="E66" r:id="rId9" display="https://algomaster.io/practice/dsa/copy-list-with-random-pointer?list=am-600" xr:uid="{09552B41-5AF7-4B01-AE0B-A467F22DACFD}"/>
+    <hyperlink ref="E67" r:id="rId10" display="https://algomaster.io/practice/dsa/partition-list?list=am-600" xr:uid="{04989643-71CA-482F-BB39-2CFDBE1A71B6}"/>
+    <hyperlink ref="E68" r:id="rId11" display="https://algomaster.io/practice/dsa/rotate-list?list=am-600" xr:uid="{C23CC4B3-8264-46DF-AB43-9403C76DE7BF}"/>
+    <hyperlink ref="E69" r:id="rId12" display="https://algomaster.io/practice/dsa/reorder-list?list=am-600" xr:uid="{807406E1-5A25-4741-BA04-C52ED3780B08}"/>
+    <hyperlink ref="E70" r:id="rId13" display="https://algomaster.io/practice/dsa/add-two-numbers?list=am-600" xr:uid="{4F17E119-77A7-4DF6-B3B0-73356FEE4206}"/>
+    <hyperlink ref="E71" r:id="rId14" display="https://algomaster.io/practice/dsa/add-two-numbers-ii?list=am-600" xr:uid="{86E548A4-3A07-4879-ABCA-CA7B6C3780D3}"/>
+    <hyperlink ref="E72" r:id="rId15" display="https://algomaster.io/practice/dsa/delete-node-in-a-linked-list?list=am-600" xr:uid="{0733E3FA-0B59-4EE8-A9ED-4712429D6DFC}"/>
+    <hyperlink ref="E73" r:id="rId16" display="https://algomaster.io/practice/dsa/flatten-a-multilevel-doubly-linked-list?list=am-600" xr:uid="{117D3E6E-F4C8-41FF-8C01-B4224E3CBE63}"/>
+    <hyperlink ref="E74" r:id="rId17" display="https://algomaster.io/practice/dsa/insert-into-a-sorted-circular-linked-list?list=am-600" xr:uid="{09BFCD13-DC60-4FAB-A546-4ED5BB4D957A}"/>
+    <hyperlink ref="E75" r:id="rId18" display="https://algomaster.io/practice/dsa/merge-in-between-linked-lists?list=am-600" xr:uid="{42CD030F-52F9-4C2A-9082-D94E28D2CCB1}"/>
+    <hyperlink ref="E77" r:id="rId19" display="https://algomaster.io/practice/dsa/palindrome-linked-list?list=am-600" xr:uid="{9DA8B1FB-33D4-4A40-BC5F-4F2F8EE1ECFC}"/>
+    <hyperlink ref="E78" r:id="rId20" display="https://algomaster.io/practice/dsa/reverse-linked-list?list=am-600" xr:uid="{AD6EC35F-76BD-4D40-B3C1-2CE12439F9FF}"/>
+    <hyperlink ref="E79" r:id="rId21" display="https://algomaster.io/practice/dsa/reverse-linked-list-ii?list=am-600" xr:uid="{9A1E539B-5B89-4FE2-918F-BAFBCB5D62DA}"/>
+    <hyperlink ref="E80" r:id="rId22" display="https://algomaster.io/practice/dsa/reverse-nodes-in-k-group?list=am-600" xr:uid="{FBA2DDE1-7F8A-40A8-8862-A6231300AE36}"/>
+    <hyperlink ref="E82" r:id="rId23" display="https://algomaster.io/practice/dsa/middle-of-the-linked-list?list=am-600" xr:uid="{6107F189-D4D4-46C4-A292-188CC944DCED}"/>
+    <hyperlink ref="E83" r:id="rId24" display="https://algomaster.io/practice/dsa/happy-number?list=am-600" xr:uid="{88745412-83ED-4A53-9CBD-F539D44A2E1A}"/>
+    <hyperlink ref="E84" r:id="rId25" display="https://algomaster.io/practice/dsa/linked-list-cycle-ii?list=am-600" xr:uid="{C26BCC0B-D165-4AA6-9AD8-06C93C6B3D63}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CDB0AB-1BCC-465D-8B08-CA5184B7DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0C2CAE-5D05-474D-9EED-37FDA81E6C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2750" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
-    <sheet name="PrefixSum" sheetId="1" r:id="rId2"/>
-    <sheet name="Sliding Window" sheetId="4" r:id="rId3"/>
-    <sheet name="LinkedList" sheetId="5" r:id="rId4"/>
-    <sheet name="Stack" sheetId="6" r:id="rId5"/>
-    <sheet name="Source" sheetId="3" r:id="rId6"/>
+    <sheet name="Order" sheetId="7" r:id="rId1"/>
+    <sheet name="Two Pointers" sheetId="2" r:id="rId2"/>
+    <sheet name="PrefixSum" sheetId="1" r:id="rId3"/>
+    <sheet name="Sliding Window" sheetId="4" r:id="rId4"/>
+    <sheet name="LinkedList" sheetId="5" r:id="rId5"/>
+    <sheet name="Stack" sheetId="6" r:id="rId6"/>
+    <sheet name="Binary Search" sheetId="8" r:id="rId7"/>
+    <sheet name="Source" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="273">
   <si>
     <t>Company Wise</t>
   </si>
@@ -544,6 +546,354 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>Middle of the linked list</t>
+  </si>
+  <si>
+    <t>linked list cycle</t>
+  </si>
+  <si>
+    <t>check LinkList is palindrome o not</t>
+  </si>
+  <si>
+    <t>pradeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Reverse polish notion</t>
+  </si>
+  <si>
+    <t>•       Decode string</t>
+  </si>
+  <si>
+    <t>•       Daily Temperatures</t>
+  </si>
+  <si>
+    <t>•       Next Greater Element</t>
+  </si>
+  <si>
+    <t>•       Largest Rectangle in Histogram</t>
+  </si>
+  <si>
+    <t>132 Pattern</t>
+  </si>
+  <si>
+    <t>Good to start</t>
+  </si>
+  <si>
+    <t>Monotonic Stack</t>
+  </si>
+  <si>
+    <t>Next Greater Element I</t>
+  </si>
+  <si>
+    <t>Next Greater Element II</t>
+  </si>
+  <si>
+    <t>Daily Temperatures</t>
+  </si>
+  <si>
+    <t>Online Stock Span</t>
+  </si>
+  <si>
+    <t>Asteroid Collision</t>
+  </si>
+  <si>
+    <t>Largest Rectangle in Histogram</t>
+  </si>
+  <si>
+    <t>Maximal Rectangle</t>
+  </si>
+  <si>
+    <t>Expression Evaluation</t>
+  </si>
+  <si>
+    <t>Basic Calculator II</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
+  </si>
+  <si>
+    <t>Decode String</t>
+  </si>
+  <si>
+    <t>Basic Calculator I</t>
+  </si>
+  <si>
+    <t>Stack Simulation/Undo Operation</t>
+  </si>
+  <si>
+    <t>Backspace String Compare</t>
+  </si>
+  <si>
+    <t>Remove All Adjacent Duplicates</t>
+  </si>
+  <si>
+    <t>Make the String Great</t>
+  </si>
+  <si>
+    <t>Minimum String Length After Removing Substrings</t>
+  </si>
+  <si>
+    <t>Parathesis &amp; Scoring</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Minimum Add to Make Parentheses Valid</t>
+  </si>
+  <si>
+    <t>Score of Parentheses</t>
+  </si>
+  <si>
+    <t>Longest Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Stack-based Design</t>
+  </si>
+  <si>
+    <t>Implement Queue using Stacks</t>
+  </si>
+  <si>
+    <t>Implement Stack using Queues</t>
+  </si>
+  <si>
+    <t>Min Stack</t>
+  </si>
+  <si>
+    <t>Max Stack</t>
+  </si>
+  <si>
+    <t>Design Stack with Increment Operation</t>
+  </si>
+  <si>
+    <t>Stack+Greedy</t>
+  </si>
+  <si>
+    <t>Remove K Digits</t>
+  </si>
+  <si>
+    <t>Remove Duplicate Letters</t>
+  </si>
+  <si>
+    <t>Smallest Subsequence of Distinct Characters</t>
+  </si>
+  <si>
+    <t>Minimum Remove to Make Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Create Maximum Number</t>
+  </si>
+  <si>
+    <t>Recursive Stack</t>
+  </si>
+  <si>
+    <t>Delete Middle Element of Stack</t>
+  </si>
+  <si>
+    <t>Reverse a Stack (Recursive)</t>
+  </si>
+  <si>
+    <t>Insert at Bottom of Stack</t>
+  </si>
+  <si>
+    <t>Stacks</t>
+  </si>
+  <si>
+    <t>Baseball Game</t>
+  </si>
+  <si>
+    <t>Remove All Adjacent Duplicates In String</t>
+  </si>
+  <si>
+    <t>Maximum Nesting Depth of the Parentheses</t>
+  </si>
+  <si>
+    <t>Car Fleet</t>
+  </si>
+  <si>
+    <t>Valid Parenthesis String</t>
+  </si>
+  <si>
+    <t>Validate Stack Sequences</t>
+  </si>
+  <si>
+    <t>Removing Stars From a String</t>
+  </si>
+  <si>
+    <t>Simplify Path</t>
+  </si>
+  <si>
+    <t>Exclusive Time of Functions</t>
+  </si>
+  <si>
+    <t>Basic Calculator</t>
+  </si>
+  <si>
+    <t>Final Prices With a Special Discount in a Shop</t>
+  </si>
+  <si>
+    <t>Buildings With an Ocean View</t>
+  </si>
+  <si>
+    <t>Maximum Width Ramp</t>
+  </si>
+  <si>
+    <t>Max Chunks To Make Sorted</t>
+  </si>
+  <si>
+    <t>Sum of Subarray Minimums</t>
+  </si>
+  <si>
+    <t>Sum of Subarray Ranges</t>
+  </si>
+  <si>
+    <t>Shortest Unsorted Continuous Subarray</t>
+  </si>
+  <si>
+    <t>Next Greater Node In Linked List</t>
+  </si>
+  <si>
+    <t>Number of Visible People in a Queue</t>
+  </si>
+  <si>
+    <t>Pradeep Order</t>
+  </si>
+  <si>
+    <t>Two Pointer</t>
+  </si>
+  <si>
+    <t>Prefix Sum</t>
+  </si>
+  <si>
+    <t>Sliding Window</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Queue</t>
+  </si>
+  <si>
+    <t>Boss Coder Order</t>
+  </si>
+  <si>
+    <t>Bit Manipulation</t>
+  </si>
+  <si>
+    <t>Searching 1 and 2</t>
+  </si>
+  <si>
+    <t>Binary Search</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Find Peak Element</t>
+  </si>
+  <si>
+    <t>Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>RisinngBrain</t>
+  </si>
+  <si>
+    <t>Structure Good For Step by step | Practise also</t>
+  </si>
+  <si>
+    <t>Classic Binary Search</t>
+  </si>
+  <si>
+    <t>Sqrt(x)</t>
+  </si>
+  <si>
+    <t>Search Insert Position</t>
+  </si>
+  <si>
+    <t>Find Minimum in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Lower/Upper Bound</t>
+  </si>
+  <si>
+    <t>Find kth rotation</t>
+  </si>
+  <si>
+    <t>Count Occurrences</t>
+  </si>
+  <si>
+    <t>Ceiling in a Sorted Array</t>
+  </si>
+  <si>
+    <t>Floor in a Sorted Array</t>
+  </si>
+  <si>
+    <t>Find First and Last Position of Element</t>
+  </si>
+  <si>
+    <t>Binary Search on Answers</t>
+  </si>
+  <si>
+    <t>Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t>Capacity To Ship Packages Within D Days</t>
+  </si>
+  <si>
+    <t>Min Speed to Arrive on Time</t>
+  </si>
+  <si>
+    <t>Aggressive cows</t>
+  </si>
+  <si>
+    <t>Magnetic Force Between Two Balls</t>
+  </si>
+  <si>
+    <t>Allocate Minimum Number of Pages</t>
+  </si>
+  <si>
+    <t>Split Array Largest Sum</t>
+  </si>
+  <si>
+    <t>Search in 2D Matrix</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix II</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element in Sorted Matrix</t>
+  </si>
+  <si>
+    <t>Matrix Median</t>
+  </si>
+  <si>
+    <t>AlgoMaster</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/binary-search/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/sqrtx/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/search-insert-position/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/search-in-rotated-sorted-array/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-minimum-in-rotated-sorted-array/description/</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/find-peak-element/description/</t>
   </si>
 </sst>
 </file>
@@ -1016,6 +1366,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8DFEBEC-A5E2-426C-B964-7E9340A42079}">
+  <dimension ref="A2:B30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C2B0EE-D568-4947-BF62-11F4617CA033}">
   <dimension ref="A2:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1045,7 +1549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:F25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1294,7 +1798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8712B1-F73E-45FE-B8C3-C6E240F961E5}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:J63"/>
@@ -1739,10 +2243,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7C268B-0F05-4BDD-888C-4499121F892A}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:G84"/>
+  <dimension ref="A2:G87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="9.36328125" customWidth="1"/>
@@ -1810,7 +2314,588 @@
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C9" s="18"/>
       <c r="E9" s="14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C10" s="18"/>
+      <c r="E10" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C11" s="18"/>
+      <c r="E11" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C12" s="18"/>
+      <c r="E12" s="14" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C14" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C15" s="18"/>
+      <c r="E15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C16" s="18"/>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C17" s="18"/>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C18" s="18"/>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C19" s="18"/>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C20" s="18"/>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C21" s="18"/>
+      <c r="E21" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C22" s="18"/>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C23" s="18"/>
+      <c r="E23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C24" s="18"/>
+      <c r="E24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C25" s="18"/>
+      <c r="E25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C26" s="18"/>
+      <c r="E26" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C27" s="18"/>
+      <c r="E27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C28" s="18"/>
+      <c r="E28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C29" s="18"/>
+      <c r="E29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C30" s="18"/>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C31" s="18"/>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C32" s="18"/>
+      <c r="E32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C33" s="18"/>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C34" s="18"/>
+      <c r="E34" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C35" s="18"/>
+      <c r="E35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C36" s="18"/>
+      <c r="E36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C37" s="18"/>
+      <c r="E37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C38" s="18"/>
+      <c r="E38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C39" s="18"/>
+      <c r="E39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C40" s="18"/>
+      <c r="E40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C41" s="18"/>
+      <c r="E41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C42" s="18"/>
+      <c r="E42" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C43" s="18"/>
+      <c r="E43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C44" s="18"/>
+      <c r="E44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C45" s="18"/>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C46" s="18"/>
+      <c r="E46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C47" s="18"/>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C48" s="18"/>
+      <c r="E48" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C49" s="18"/>
+      <c r="E49" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C50" s="18"/>
+      <c r="E50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C51" s="18"/>
+      <c r="E51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C52" s="18"/>
+      <c r="E52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C53" s="18"/>
+      <c r="E53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C54" s="18"/>
+      <c r="E54" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C55" s="18"/>
+      <c r="E55" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C56" s="18"/>
+      <c r="E56" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C57" s="18"/>
+      <c r="E57" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C58" s="18"/>
+      <c r="E58" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C59" s="18"/>
+      <c r="E59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C61" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C62" s="18"/>
+      <c r="E62" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C63" s="18"/>
+      <c r="E63" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C64" s="18"/>
+      <c r="E64" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C65" s="18"/>
+      <c r="E65" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C66" s="18"/>
+      <c r="E66" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C67" s="18"/>
+      <c r="E67" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C68" s="18"/>
+      <c r="E68" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C69" s="18"/>
+      <c r="E69" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C70" s="18"/>
+      <c r="E70" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C71" s="18"/>
+      <c r="E71" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C72" s="18"/>
+      <c r="E72" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C73" s="18"/>
+      <c r="E73" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C74" s="18"/>
+      <c r="E74" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C75" s="18"/>
+      <c r="E75" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C76" s="18"/>
+      <c r="E76" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C77" s="18"/>
+      <c r="E77" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C78" s="18"/>
+      <c r="E78" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C79" s="18"/>
+      <c r="E79" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C80" s="18"/>
+      <c r="E80" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C81" s="18"/>
+      <c r="E81" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C82" s="18"/>
+      <c r="E82" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C83" s="18"/>
+      <c r="E83" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C84" s="18"/>
+      <c r="E84" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C85" s="18"/>
+      <c r="E85" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C86" s="18"/>
+      <c r="E86" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C87" s="18"/>
+      <c r="E87" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:C12"/>
+    <mergeCell ref="C14:C59"/>
+    <mergeCell ref="C61:C87"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E61" r:id="rId1" display="https://algomaster.io/practice/dsa/intersection-of-two-linked-lists?list=am-600" xr:uid="{804095C8-0F1F-431B-AFFA-9049A574F9C2}"/>
+    <hyperlink ref="E62" r:id="rId2" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list?list=am-600" xr:uid="{22500AE3-3119-4C8A-B101-B6EF3E5F28F7}"/>
+    <hyperlink ref="E63" r:id="rId3" display="https://algomaster.io/practice/dsa/design-linked-list?list=am-600" xr:uid="{0A27B262-F4FB-4CA5-AF8B-FCED30D27874}"/>
+    <hyperlink ref="E64" r:id="rId4" display="https://algomaster.io/practice/dsa/delete-the-middle-node-of-a-linked-list?list=am-600" xr:uid="{487BFEA0-A6C3-4865-984D-84FF2576F3B7}"/>
+    <hyperlink ref="E65" r:id="rId5" display="https://algomaster.io/practice/dsa/remove-nth-node-from-end-of-list?list=am-600" xr:uid="{44428435-57A0-4B31-A499-462B0FE3B5AA}"/>
+    <hyperlink ref="E66" r:id="rId6" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list-ii?list=am-600" xr:uid="{0F5F3F7B-28F8-4DDA-ACD5-EC0BF47970D1}"/>
+    <hyperlink ref="E67" r:id="rId7" display="https://algomaster.io/practice/dsa/odd-even-linked-list?list=am-600" xr:uid="{FC921715-4514-4657-822C-6E1E6B015430}"/>
+    <hyperlink ref="E68" r:id="rId8" display="https://algomaster.io/practice/dsa/swap-nodes-in-pairs?list=am-600" xr:uid="{1C2D3151-2C70-432E-81FB-9EAC732DF921}"/>
+    <hyperlink ref="E69" r:id="rId9" display="https://algomaster.io/practice/dsa/copy-list-with-random-pointer?list=am-600" xr:uid="{09552B41-5AF7-4B01-AE0B-A467F22DACFD}"/>
+    <hyperlink ref="E70" r:id="rId10" display="https://algomaster.io/practice/dsa/partition-list?list=am-600" xr:uid="{04989643-71CA-482F-BB39-2CFDBE1A71B6}"/>
+    <hyperlink ref="E71" r:id="rId11" display="https://algomaster.io/practice/dsa/rotate-list?list=am-600" xr:uid="{C23CC4B3-8264-46DF-AB43-9403C76DE7BF}"/>
+    <hyperlink ref="E72" r:id="rId12" display="https://algomaster.io/practice/dsa/reorder-list?list=am-600" xr:uid="{807406E1-5A25-4741-BA04-C52ED3780B08}"/>
+    <hyperlink ref="E73" r:id="rId13" display="https://algomaster.io/practice/dsa/add-two-numbers?list=am-600" xr:uid="{4F17E119-77A7-4DF6-B3B0-73356FEE4206}"/>
+    <hyperlink ref="E74" r:id="rId14" display="https://algomaster.io/practice/dsa/add-two-numbers-ii?list=am-600" xr:uid="{86E548A4-3A07-4879-ABCA-CA7B6C3780D3}"/>
+    <hyperlink ref="E75" r:id="rId15" display="https://algomaster.io/practice/dsa/delete-node-in-a-linked-list?list=am-600" xr:uid="{0733E3FA-0B59-4EE8-A9ED-4712429D6DFC}"/>
+    <hyperlink ref="E76" r:id="rId16" display="https://algomaster.io/practice/dsa/flatten-a-multilevel-doubly-linked-list?list=am-600" xr:uid="{117D3E6E-F4C8-41FF-8C01-B4224E3CBE63}"/>
+    <hyperlink ref="E77" r:id="rId17" display="https://algomaster.io/practice/dsa/insert-into-a-sorted-circular-linked-list?list=am-600" xr:uid="{09BFCD13-DC60-4FAB-A546-4ED5BB4D957A}"/>
+    <hyperlink ref="E78" r:id="rId18" display="https://algomaster.io/practice/dsa/merge-in-between-linked-lists?list=am-600" xr:uid="{42CD030F-52F9-4C2A-9082-D94E28D2CCB1}"/>
+    <hyperlink ref="E80" r:id="rId19" display="https://algomaster.io/practice/dsa/palindrome-linked-list?list=am-600" xr:uid="{9DA8B1FB-33D4-4A40-BC5F-4F2F8EE1ECFC}"/>
+    <hyperlink ref="E81" r:id="rId20" display="https://algomaster.io/practice/dsa/reverse-linked-list?list=am-600" xr:uid="{AD6EC35F-76BD-4D40-B3C1-2CE12439F9FF}"/>
+    <hyperlink ref="E82" r:id="rId21" display="https://algomaster.io/practice/dsa/reverse-linked-list-ii?list=am-600" xr:uid="{9A1E539B-5B89-4FE2-918F-BAFBCB5D62DA}"/>
+    <hyperlink ref="E83" r:id="rId22" display="https://algomaster.io/practice/dsa/reverse-nodes-in-k-group?list=am-600" xr:uid="{FBA2DDE1-7F8A-40A8-8862-A6231300AE36}"/>
+    <hyperlink ref="E85" r:id="rId23" display="https://algomaster.io/practice/dsa/middle-of-the-linked-list?list=am-600" xr:uid="{6107F189-D4D4-46C4-A292-188CC944DCED}"/>
+    <hyperlink ref="E86" r:id="rId24" display="https://algomaster.io/practice/dsa/happy-number?list=am-600" xr:uid="{88745412-83ED-4A53-9CBD-F539D44A2E1A}"/>
+    <hyperlink ref="E87" r:id="rId25" display="https://algomaster.io/practice/dsa/linked-list-cycle-ii?list=am-600" xr:uid="{C26BCC0B-D165-4AA6-9AD8-06C93C6B3D63}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAEF6E5-7B71-4679-AA65-7B980562DC80}">
+  <dimension ref="A2:G87"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="21.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E9" s="14" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1820,499 +2905,453 @@
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C11" s="18" t="s">
+      <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>100</v>
+        <v>169</v>
+      </c>
+      <c r="G11" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="18"/>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C13" s="18"/>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C14" s="18"/>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C15" s="18"/>
       <c r="E15" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C16" s="18"/>
       <c r="E16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C17" s="18"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C18" s="18"/>
-      <c r="E18" s="15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C19" s="18"/>
-      <c r="E19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C20" s="18"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E19" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C21" s="18"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C22" s="18"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C23" s="18"/>
-      <c r="E23" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C24" s="18"/>
-      <c r="E24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C25" s="18"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E24" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C26" s="18"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C27" s="18"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E27" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C28" s="18"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C29" s="18"/>
-      <c r="E29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C30" s="18"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E29" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C31" s="18"/>
-      <c r="E31" s="15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C32" s="18"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="18"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="18"/>
-      <c r="E34" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="18"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E34" s="15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="18"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="18"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="18"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="18"/>
-      <c r="E39" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="18"/>
-      <c r="E40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="18"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E40" s="15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="18"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="18"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E43" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="18"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="18"/>
-      <c r="E45" s="15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="18"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E45" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E46" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="18"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E47" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="18"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C49" s="18"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E49" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C50" s="18"/>
-      <c r="E50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C51" s="18"/>
-      <c r="E51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C52" s="18"/>
-      <c r="E52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C53" s="18"/>
-      <c r="E53" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C54" s="18"/>
-      <c r="E54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C55" s="18"/>
-      <c r="E55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C56" s="18"/>
-      <c r="E56" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C58" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
         <v>8</v>
       </c>
+      <c r="E51" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E52" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E53" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E54" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E55" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E56" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E57" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E58" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C59" s="18"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E59" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C60" s="18"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E60" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C61" s="18"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E61" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C62" s="18"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E62" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C63" s="18"/>
-      <c r="E63" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C64" s="18"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="E63" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="E64" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C65" s="18"/>
-      <c r="E65" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C66" s="18"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E65" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E66" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C67" s="18"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E67" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C68" s="18"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="68" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E68" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C69" s="18"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E69" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="70" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C70" s="18"/>
-      <c r="E70" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C71" s="18"/>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E70" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E71" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C72" s="18"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E72" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C73" s="18"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E73" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C74" s="18"/>
-      <c r="E74" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C75" s="18"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E74" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E75" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C76" s="18"/>
-      <c r="E76" s="15" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C77" s="18"/>
-      <c r="E77" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C78" s="18"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="76" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E76" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="77" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E77" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E78" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C79" s="18"/>
-      <c r="E79" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="80" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C80" s="18"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="79" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E79" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="80" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E80" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C81" s="18"/>
-      <c r="E81" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C82" s="18"/>
-      <c r="E82" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C83" s="18"/>
-      <c r="E83" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="84" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C84" s="18"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E81" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E82" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E83" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E84" s="1" t="s">
-        <v>110</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E85" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="E86" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E87" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="C11:C56"/>
-    <mergeCell ref="C58:C84"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E58" r:id="rId1" display="https://algomaster.io/practice/dsa/intersection-of-two-linked-lists?list=am-600" xr:uid="{804095C8-0F1F-431B-AFFA-9049A574F9C2}"/>
-    <hyperlink ref="E59" r:id="rId2" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list?list=am-600" xr:uid="{22500AE3-3119-4C8A-B101-B6EF3E5F28F7}"/>
-    <hyperlink ref="E60" r:id="rId3" display="https://algomaster.io/practice/dsa/design-linked-list?list=am-600" xr:uid="{0A27B262-F4FB-4CA5-AF8B-FCED30D27874}"/>
-    <hyperlink ref="E61" r:id="rId4" display="https://algomaster.io/practice/dsa/delete-the-middle-node-of-a-linked-list?list=am-600" xr:uid="{487BFEA0-A6C3-4865-984D-84FF2576F3B7}"/>
-    <hyperlink ref="E62" r:id="rId5" display="https://algomaster.io/practice/dsa/remove-nth-node-from-end-of-list?list=am-600" xr:uid="{44428435-57A0-4B31-A499-462B0FE3B5AA}"/>
-    <hyperlink ref="E63" r:id="rId6" display="https://algomaster.io/practice/dsa/remove-duplicates-from-sorted-list-ii?list=am-600" xr:uid="{0F5F3F7B-28F8-4DDA-ACD5-EC0BF47970D1}"/>
-    <hyperlink ref="E64" r:id="rId7" display="https://algomaster.io/practice/dsa/odd-even-linked-list?list=am-600" xr:uid="{FC921715-4514-4657-822C-6E1E6B015430}"/>
-    <hyperlink ref="E65" r:id="rId8" display="https://algomaster.io/practice/dsa/swap-nodes-in-pairs?list=am-600" xr:uid="{1C2D3151-2C70-432E-81FB-9EAC732DF921}"/>
-    <hyperlink ref="E66" r:id="rId9" display="https://algomaster.io/practice/dsa/copy-list-with-random-pointer?list=am-600" xr:uid="{09552B41-5AF7-4B01-AE0B-A467F22DACFD}"/>
-    <hyperlink ref="E67" r:id="rId10" display="https://algomaster.io/practice/dsa/partition-list?list=am-600" xr:uid="{04989643-71CA-482F-BB39-2CFDBE1A71B6}"/>
-    <hyperlink ref="E68" r:id="rId11" display="https://algomaster.io/practice/dsa/rotate-list?list=am-600" xr:uid="{C23CC4B3-8264-46DF-AB43-9403C76DE7BF}"/>
-    <hyperlink ref="E69" r:id="rId12" display="https://algomaster.io/practice/dsa/reorder-list?list=am-600" xr:uid="{807406E1-5A25-4741-BA04-C52ED3780B08}"/>
-    <hyperlink ref="E70" r:id="rId13" display="https://algomaster.io/practice/dsa/add-two-numbers?list=am-600" xr:uid="{4F17E119-77A7-4DF6-B3B0-73356FEE4206}"/>
-    <hyperlink ref="E71" r:id="rId14" display="https://algomaster.io/practice/dsa/add-two-numbers-ii?list=am-600" xr:uid="{86E548A4-3A07-4879-ABCA-CA7B6C3780D3}"/>
-    <hyperlink ref="E72" r:id="rId15" display="https://algomaster.io/practice/dsa/delete-node-in-a-linked-list?list=am-600" xr:uid="{0733E3FA-0B59-4EE8-A9ED-4712429D6DFC}"/>
-    <hyperlink ref="E73" r:id="rId16" display="https://algomaster.io/practice/dsa/flatten-a-multilevel-doubly-linked-list?list=am-600" xr:uid="{117D3E6E-F4C8-41FF-8C01-B4224E3CBE63}"/>
-    <hyperlink ref="E74" r:id="rId17" display="https://algomaster.io/practice/dsa/insert-into-a-sorted-circular-linked-list?list=am-600" xr:uid="{09BFCD13-DC60-4FAB-A546-4ED5BB4D957A}"/>
-    <hyperlink ref="E75" r:id="rId18" display="https://algomaster.io/practice/dsa/merge-in-between-linked-lists?list=am-600" xr:uid="{42CD030F-52F9-4C2A-9082-D94E28D2CCB1}"/>
-    <hyperlink ref="E77" r:id="rId19" display="https://algomaster.io/practice/dsa/palindrome-linked-list?list=am-600" xr:uid="{9DA8B1FB-33D4-4A40-BC5F-4F2F8EE1ECFC}"/>
-    <hyperlink ref="E78" r:id="rId20" display="https://algomaster.io/practice/dsa/reverse-linked-list?list=am-600" xr:uid="{AD6EC35F-76BD-4D40-B3C1-2CE12439F9FF}"/>
-    <hyperlink ref="E79" r:id="rId21" display="https://algomaster.io/practice/dsa/reverse-linked-list-ii?list=am-600" xr:uid="{9A1E539B-5B89-4FE2-918F-BAFBCB5D62DA}"/>
-    <hyperlink ref="E80" r:id="rId22" display="https://algomaster.io/practice/dsa/reverse-nodes-in-k-group?list=am-600" xr:uid="{FBA2DDE1-7F8A-40A8-8862-A6231300AE36}"/>
-    <hyperlink ref="E82" r:id="rId23" display="https://algomaster.io/practice/dsa/middle-of-the-linked-list?list=am-600" xr:uid="{6107F189-D4D4-46C4-A292-188CC944DCED}"/>
-    <hyperlink ref="E83" r:id="rId24" display="https://algomaster.io/practice/dsa/happy-number?list=am-600" xr:uid="{88745412-83ED-4A53-9CBD-F539D44A2E1A}"/>
-    <hyperlink ref="E84" r:id="rId25" display="https://algomaster.io/practice/dsa/linked-list-cycle-ii?list=am-600" xr:uid="{C26BCC0B-D165-4AA6-9AD8-06C93C6B3D63}"/>
+    <hyperlink ref="E52" r:id="rId1" display="https://algomaster.io/practice/dsa/valid-parentheses?list=am-600" xr:uid="{BD48A660-E5F7-417C-ABC4-943950DA0927}"/>
+    <hyperlink ref="E53" r:id="rId2" display="https://algomaster.io/practice/dsa/baseball-game?list=am-600" xr:uid="{E020FEEE-9CCA-42A6-9EDE-D84749F2CCF0}"/>
+    <hyperlink ref="E54" r:id="rId3" display="https://algomaster.io/practice/dsa/remove-all-adjacent-duplicates-in-string?list=am-600" xr:uid="{20B04465-C584-4B16-9679-12B40BAAF5C1}"/>
+    <hyperlink ref="E55" r:id="rId4" display="https://algomaster.io/practice/dsa/maximum-nesting-depth-of-the-parentheses?list=am-600" xr:uid="{3B05F4C3-9958-4613-A018-843748BB113C}"/>
+    <hyperlink ref="E56" r:id="rId5" display="https://algomaster.io/practice/dsa/min-stack?list=am-600" xr:uid="{BEA9C666-C865-42A2-A1A3-78C05A986CA0}"/>
+    <hyperlink ref="E57" r:id="rId6" display="https://algomaster.io/practice/dsa/asteroid-collision?list=am-600" xr:uid="{A561B922-5E72-4EAB-A54D-98CF3B51AC45}"/>
+    <hyperlink ref="E58" r:id="rId7" display="https://algomaster.io/practice/dsa/car-fleet?list=am-600" xr:uid="{A34800F6-34DC-4CFC-B236-6B7FC333D115}"/>
+    <hyperlink ref="E59" r:id="rId8" display="https://algomaster.io/practice/dsa/valid-parenthesis-string?list=am-600" xr:uid="{0AF7EA4A-0CB7-4C80-B3D3-3A7E4FFC22C8}"/>
+    <hyperlink ref="E60" r:id="rId9" display="https://algomaster.io/practice/dsa/validate-stack-sequences?list=am-600" xr:uid="{33E11C7C-6D6C-4451-954D-FADB13DBEEE2}"/>
+    <hyperlink ref="E61" r:id="rId10" display="https://algomaster.io/practice/dsa/minimum-remove-to-make-valid-parentheses?list=am-600" xr:uid="{7C599CCA-08DE-44D0-9244-E80E7EEB3FD2}"/>
+    <hyperlink ref="E62" r:id="rId11" display="https://algomaster.io/practice/dsa/remove-duplicate-letters?list=am-600" xr:uid="{3D501A69-FF2F-4EB3-B431-2F3B16C77243}"/>
+    <hyperlink ref="E63" r:id="rId12" display="https://algomaster.io/practice/dsa/removing-stars-from-a-string?list=am-600" xr:uid="{17138A7C-5A10-47B8-89DF-739C7220497B}"/>
+    <hyperlink ref="E64" r:id="rId13" display="https://algomaster.io/practice/dsa/simplify-path?list=am-600" xr:uid="{8114834E-BB79-4D24-8433-C6BCF2BA9610}"/>
+    <hyperlink ref="E65" r:id="rId14" display="https://algomaster.io/practice/dsa/exclusive-time-of-functions?list=am-600" xr:uid="{46715422-717C-4EAA-BCDF-53DDB9E30B32}"/>
+    <hyperlink ref="E66" r:id="rId15" display="https://algomaster.io/practice/dsa/evaluate-reverse-polish-notation?list=am-600" xr:uid="{A0A9F060-0B34-4500-BCC2-F8630C5D5D02}"/>
+    <hyperlink ref="E67" r:id="rId16" display="https://algomaster.io/practice/dsa/basic-calculator-ii?list=am-600" xr:uid="{AA8C5045-DA00-4B83-9CE3-877499541EEE}"/>
+    <hyperlink ref="E68" r:id="rId17" display="https://algomaster.io/practice/dsa/basic-calculator?list=am-600" xr:uid="{0F2229EA-8477-4C1D-8273-60F60E480E56}"/>
+    <hyperlink ref="E69" r:id="rId18" display="https://algomaster.io/practice/dsa/longest-valid-parentheses?list=am-600" xr:uid="{CA19973D-E95E-4EEF-B61C-6D6179E889A1}"/>
+    <hyperlink ref="E71" r:id="rId19" display="https://algomaster.io/practice/dsa/next-greater-element-i?list=am-600" xr:uid="{C8745DE2-06A3-45A9-AF1B-837AC5550E8C}"/>
+    <hyperlink ref="E72" r:id="rId20" display="https://algomaster.io/practice/dsa/final-prices-with-a-special-discount-in-a-shop?list=am-600" xr:uid="{1ED5F7FB-EF32-4CF5-B112-3C3546CC84E4}"/>
+    <hyperlink ref="E73" r:id="rId21" display="https://algomaster.io/practice/dsa/next-greater-element-ii?list=am-600" xr:uid="{350BD5F4-D646-4577-9395-4BC2BB85932C}"/>
+    <hyperlink ref="E74" r:id="rId22" display="https://algomaster.io/practice/dsa/daily-temperatures?list=am-600" xr:uid="{CC39A0A5-6A1A-4BF6-B339-C3EBBDCA3689}"/>
+    <hyperlink ref="E75" r:id="rId23" display="https://algomaster.io/practice/dsa/online-stock-span?list=am-600" xr:uid="{5BAFB6EC-0A9A-45E1-A9DC-9D26EF144585}"/>
+    <hyperlink ref="E76" r:id="rId24" display="https://algomaster.io/practice/dsa/buildings-with-an-ocean-view?list=am-600" xr:uid="{F96DF91C-3FF7-4FA4-BF50-15283C7DA14E}"/>
+    <hyperlink ref="E77" r:id="rId25" display="https://algomaster.io/practice/dsa/132-pattern?list=am-600" xr:uid="{C3E4B55E-61E2-4CA1-AF42-011725405616}"/>
+    <hyperlink ref="E78" r:id="rId26" display="https://algomaster.io/practice/dsa/remove-k-digits?list=am-600" xr:uid="{A2985CE5-851A-4A71-A2EE-BA819B9AE148}"/>
+    <hyperlink ref="E79" r:id="rId27" display="https://algomaster.io/practice/dsa/maximum-width-ramp?list=am-600" xr:uid="{64C6E4D1-2866-448A-B6F2-291A0DF64D5F}"/>
+    <hyperlink ref="E80" r:id="rId28" display="https://algomaster.io/practice/dsa/max-chunks-to-make-sorted?list=am-600" xr:uid="{64F8EF01-96FF-4989-A7AE-E7E03DB8ABF3}"/>
+    <hyperlink ref="E81" r:id="rId29" display="https://algomaster.io/practice/dsa/sum-of-subarray-minimums?list=am-600" xr:uid="{F1B11487-A485-49BB-8A33-8D91009A0393}"/>
+    <hyperlink ref="E82" r:id="rId30" display="https://algomaster.io/practice/dsa/sum-of-subarray-ranges?list=am-600" xr:uid="{92E8533E-B1C0-4889-9DE1-F1B7BA0F82B6}"/>
+    <hyperlink ref="E83" r:id="rId31" display="https://algomaster.io/practice/dsa/shortest-unsorted-continuous-subarray?list=am-600" xr:uid="{1F7A6C74-CCF6-4897-8D94-FD40724AD4E5}"/>
+    <hyperlink ref="E84" r:id="rId32" display="https://algomaster.io/practice/dsa/next-greater-node-in-linked-list?list=am-600" xr:uid="{4C4A9571-CBBB-4D53-AFF0-D47C5A2C6E04}"/>
+    <hyperlink ref="E85" r:id="rId33" display="https://algomaster.io/practice/dsa/number-of-visible-people-in-a-queue?list=am-600" xr:uid="{15CD4A03-F9E6-4EE5-900B-8D7BA50DA9E4}"/>
+    <hyperlink ref="E86" r:id="rId34" display="https://algomaster.io/practice/dsa/largest-rectangle-in-histogram?list=am-600" xr:uid="{3EA57AF4-8A20-4017-B89A-D011F9351779}"/>
+    <hyperlink ref="E87" r:id="rId35" display="https://algomaster.io/practice/dsa/create-maximum-number?list=am-600" xr:uid="{8DE3AA28-E2FE-42A8-9A07-E8B722AA2707}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CAEF6E5-7B71-4679-AA65-7B980562DC80}">
-  <dimension ref="A2:F2"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97DB269-7E8D-4F8A-91F3-657888A46C31}">
+  <dimension ref="A2:F35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="34.7265625" customWidth="1"/>
+    <col min="6" max="6" width="30.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -2334,21 +3373,243 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E6" s="14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F13" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E15" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E21" s="15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E23" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E29" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E30" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E31" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E32" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E33" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A4341A-8970-49E7-87F8-7C27F48C50D8}">
-  <dimension ref="A2:B17"/>
+  <dimension ref="A2:C17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" customWidth="1"/>
     <col min="2" max="2" width="65.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2356,15 +3617,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2372,7 +3636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2380,7 +3644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2388,7 +3652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2396,7 +3660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>51</v>
       </c>

--- a/Shreyash DSA Sheet.xlsx
+++ b/Shreyash DSA Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0C2CAE-5D05-474D-9EED-37FDA81E6C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2C80C1-6503-44AC-84ED-7DD6F2A1043B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="1820" windowWidth="14400" windowHeight="8260" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Order" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="304">
   <si>
     <t>Company Wise</t>
   </si>
@@ -875,9 +875,6 @@
     <t>Matrix Median</t>
   </si>
   <si>
-    <t>AlgoMaster</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/binary-search/description/</t>
   </si>
   <si>
@@ -894,13 +891,169 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/find-peak-element/description/</t>
+  </si>
+  <si>
+    <t>•       Two Sum II</t>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1B5E20"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Container With Most Water</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1B5E20"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3Sum</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1B5E20"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Remove Duplicates from Sorted Array</t>
+    </r>
+  </si>
+  <si>
+    <t>Valid Palindrome</t>
+  </si>
+  <si>
+    <t>Rising Brain</t>
+  </si>
+  <si>
+    <t>Arrays</t>
+  </si>
+  <si>
+    <t>Move Zeroes</t>
+  </si>
+  <si>
+    <t>Two Sum II</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <t>Sort Colors</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Trapping Rain Water</t>
+  </si>
+  <si>
+    <t>String Palindrome</t>
+  </si>
+  <si>
+    <t>Reverse a String</t>
+  </si>
+  <si>
+    <t>Valid Palindrome II</t>
+  </si>
+  <si>
+    <t>Longest Palindromic Substring</t>
+  </si>
+  <si>
+    <t>Palindromic Substrings</t>
+  </si>
+  <si>
+    <t>First Bad Version</t>
+  </si>
+  <si>
+    <t>Valid Perfect Square</t>
+  </si>
+  <si>
+    <t>Guess Number Higher or Lower</t>
+  </si>
+  <si>
+    <t>Find Smallest Letter Greater Than Target</t>
+  </si>
+  <si>
+    <t>Find First and Last Position of Element in Sorted Array</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array II</t>
+  </si>
+  <si>
+    <t>Random Pick with Weight</t>
+  </si>
+  <si>
+    <t>Find K Closest Elements</t>
+  </si>
+  <si>
+    <t>Heaters</t>
+  </si>
+  <si>
+    <t>Minimum Number of Days to Make m Bouquets</t>
+  </si>
+  <si>
+    <t>Find in Mountain Array</t>
+  </si>
+  <si>
+    <t>Find K-th Smallest Pair Distance</t>
+  </si>
+  <si>
+    <t>Recursion</t>
+  </si>
+  <si>
+    <t>Backtracking</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,6 +1135,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1046,7 +1216,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1080,6 +1250,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1503,10 +1676,16 @@
       <c r="A28">
         <v>5</v>
       </c>
+      <c r="B28" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -1521,10 +1700,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C2B0EE-D568-4947-BF62-11F4617CA033}">
-  <dimension ref="A2:F2"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A2:G25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="24.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1544,8 +1727,123 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E4" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E5" s="13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E6" s="13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E7" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E12" s="17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E13" s="17" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E14" s="17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E15" s="17" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E16" s="18" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E17" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E18" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E19" s="17" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E20" s="17" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E21" s="17" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E22" s="17" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E23" s="17" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1585,7 +1883,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
@@ -1596,7 +1894,7 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="C5" s="18"/>
+      <c r="C5" s="21"/>
       <c r="E5" t="s">
         <v>19</v>
       </c>
@@ -1605,7 +1903,7 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="21"/>
       <c r="E6" t="s">
         <v>20</v>
       </c>
@@ -1614,7 +1912,7 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="21"/>
       <c r="E7" t="s">
         <v>21</v>
       </c>
@@ -1628,7 +1926,7 @@
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="21" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1639,7 +1937,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="18"/>
+      <c r="C10" s="21"/>
       <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
@@ -1648,7 +1946,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="18"/>
+      <c r="C11" s="21"/>
       <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
@@ -1657,7 +1955,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="18"/>
+      <c r="C12" s="21"/>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
@@ -1666,7 +1964,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C13" s="18"/>
+      <c r="C13" s="21"/>
       <c r="E13" s="7" t="s">
         <v>31</v>
       </c>
@@ -1831,7 +2129,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
@@ -1842,7 +2140,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C4" s="18"/>
+      <c r="C4" s="21"/>
       <c r="D4" t="s">
         <v>156</v>
       </c>
@@ -1851,19 +2149,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="18"/>
+      <c r="C5" s="21"/>
       <c r="E5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="18"/>
+      <c r="C6" s="21"/>
       <c r="E6" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="18"/>
+      <c r="C7" s="21"/>
       <c r="D7" t="s">
         <v>156</v>
       </c>
@@ -1872,7 +2170,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C8" s="18"/>
+      <c r="C8" s="21"/>
       <c r="D8" t="s">
         <v>156</v>
       </c>
@@ -1881,7 +2179,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C9" s="18"/>
+      <c r="C9" s="21"/>
       <c r="D9" t="s">
         <v>156</v>
       </c>
@@ -1890,7 +2188,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" s="18"/>
+      <c r="C10" s="21"/>
       <c r="D10" t="s">
         <v>156</v>
       </c>
@@ -1899,7 +2197,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="18"/>
+      <c r="C11" s="21"/>
       <c r="D11" t="s">
         <v>156</v>
       </c>
@@ -1908,7 +2206,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C12" s="18"/>
+      <c r="C12" s="21"/>
       <c r="D12" t="s">
         <v>156</v>
       </c>
@@ -1925,7 +2223,7 @@
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="21" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="15" t="s">
@@ -1933,7 +2231,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C15" s="18"/>
+      <c r="C15" s="21"/>
       <c r="D15" t="s">
         <v>156</v>
       </c>
@@ -1942,7 +2240,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C16" s="18"/>
+      <c r="C16" s="21"/>
       <c r="D16" t="s">
         <v>156</v>
       </c>
@@ -1951,49 +2249,49 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="18"/>
+      <c r="C17" s="21"/>
       <c r="E17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C18" s="18"/>
+      <c r="C18" s="21"/>
       <c r="E18" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C19" s="18"/>
+      <c r="C19" s="21"/>
       <c r="E19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C20" s="18"/>
+      <c r="C20" s="21"/>
       <c r="E20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C21" s="18"/>
+      <c r="C21" s="21"/>
       <c r="E21" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C22" s="18"/>
+      <c r="C22" s="21"/>
       <c r="E22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C23" s="18"/>
+      <c r="C23" s="21"/>
       <c r="E23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C24" s="18"/>
+      <c r="C24" s="21"/>
       <c r="D24" t="s">
         <v>156</v>
       </c>
@@ -2002,31 +2300,31 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C25" s="18"/>
+      <c r="C25" s="21"/>
       <c r="E25" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C26" s="18"/>
+      <c r="C26" s="21"/>
       <c r="E26" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C27" s="18"/>
+      <c r="C27" s="21"/>
       <c r="E27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C28" s="18"/>
+      <c r="C28" s="21"/>
       <c r="E28" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C29" s="18"/>
+      <c r="C29" s="21"/>
       <c r="E29" t="s">
         <v>73</v>
       </c>
@@ -2044,7 +2342,7 @@
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="21" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="15" t="s">
@@ -2052,7 +2350,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C32" s="18"/>
+      <c r="C32" s="21"/>
       <c r="D32" t="s">
         <v>156</v>
       </c>
@@ -2061,7 +2359,7 @@
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="18"/>
+      <c r="C33" s="21"/>
       <c r="D33" t="s">
         <v>156</v>
       </c>
@@ -2070,37 +2368,37 @@
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="18"/>
+      <c r="C34" s="21"/>
       <c r="E34" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="18"/>
+      <c r="C35" s="21"/>
       <c r="E35" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="18"/>
+      <c r="C36" s="21"/>
       <c r="E36" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="18"/>
+      <c r="C37" s="21"/>
       <c r="E37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="18"/>
+      <c r="C38" s="21"/>
       <c r="E38" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="18"/>
+      <c r="C39" s="21"/>
       <c r="D39" t="s">
         <v>156</v>
       </c>
@@ -2109,19 +2407,19 @@
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="18"/>
+      <c r="C40" s="21"/>
       <c r="E40" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="18"/>
+      <c r="C41" s="21"/>
       <c r="E41" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="18"/>
+      <c r="C42" s="21"/>
       <c r="D42" t="s">
         <v>156</v>
       </c>
@@ -2130,61 +2428,61 @@
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="18"/>
+      <c r="C43" s="21"/>
       <c r="E43" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="18"/>
+      <c r="C44" s="21"/>
       <c r="E44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="18"/>
+      <c r="C45" s="21"/>
       <c r="E45" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="18"/>
+      <c r="C46" s="21"/>
       <c r="E46" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="18"/>
+      <c r="C47" s="21"/>
       <c r="E47" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="18"/>
+      <c r="C48" s="21"/>
       <c r="E48" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C49" s="18"/>
+      <c r="C49" s="21"/>
       <c r="E49" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C50" s="18"/>
+      <c r="C50" s="21"/>
       <c r="E50" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C51" s="18"/>
+      <c r="C51" s="21"/>
       <c r="E51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C52" s="18"/>
+      <c r="C52" s="21"/>
       <c r="E52" s="1" t="s">
         <v>88</v>
       </c>
@@ -2274,7 +2572,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
@@ -2282,55 +2580,55 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C4" s="18"/>
+      <c r="C4" s="21"/>
       <c r="E4" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C5" s="18"/>
+      <c r="C5" s="21"/>
       <c r="E5" s="14" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C6" s="18"/>
+      <c r="C6" s="21"/>
       <c r="E6" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C7" s="18"/>
+      <c r="C7" s="21"/>
       <c r="E7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C8" s="18"/>
+      <c r="C8" s="21"/>
       <c r="E8" s="14" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C9" s="18"/>
+      <c r="C9" s="21"/>
       <c r="E9" s="14" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C10" s="18"/>
+      <c r="C10" s="21"/>
       <c r="E10" s="14" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C11" s="18"/>
+      <c r="C11" s="21"/>
       <c r="E11" s="14" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="18"/>
+      <c r="C12" s="21"/>
       <c r="E12" s="14" t="s">
         <v>99</v>
       </c>
@@ -2345,7 +2643,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="21" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="15" t="s">
@@ -2353,271 +2651,271 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C15" s="18"/>
+      <c r="C15" s="21"/>
       <c r="E15" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C16" s="18"/>
+      <c r="C16" s="21"/>
       <c r="E16" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C17" s="18"/>
+      <c r="C17" s="21"/>
       <c r="E17" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C18" s="18"/>
+      <c r="C18" s="21"/>
       <c r="E18" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C19" s="18"/>
+      <c r="C19" s="21"/>
       <c r="E19" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C20" s="18"/>
+      <c r="C20" s="21"/>
       <c r="E20" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C21" s="18"/>
+      <c r="C21" s="21"/>
       <c r="E21" s="15" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C22" s="18"/>
+      <c r="C22" s="21"/>
       <c r="E22" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C23" s="18"/>
+      <c r="C23" s="21"/>
       <c r="E23" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C24" s="18"/>
+      <c r="C24" s="21"/>
       <c r="E24" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C25" s="18"/>
+      <c r="C25" s="21"/>
       <c r="E25" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="26" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C26" s="18"/>
+      <c r="C26" s="21"/>
       <c r="E26" s="15" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="27" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C27" s="18"/>
+      <c r="C27" s="21"/>
       <c r="E27" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="28" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C28" s="18"/>
+      <c r="C28" s="21"/>
       <c r="E28" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C29" s="18"/>
+      <c r="C29" s="21"/>
       <c r="E29" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="30" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C30" s="18"/>
+      <c r="C30" s="21"/>
       <c r="E30" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="31" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C31" s="18"/>
+      <c r="C31" s="21"/>
       <c r="E31" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="32" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C32" s="18"/>
+      <c r="C32" s="21"/>
       <c r="E32" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="18"/>
+      <c r="C33" s="21"/>
       <c r="E33" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="18"/>
+      <c r="C34" s="21"/>
       <c r="E34" s="15" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="18"/>
+      <c r="C35" s="21"/>
       <c r="E35" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="18"/>
+      <c r="C36" s="21"/>
       <c r="E36" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C37" s="18"/>
+      <c r="C37" s="21"/>
       <c r="E37" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C38" s="18"/>
+      <c r="C38" s="21"/>
       <c r="E38" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C39" s="18"/>
+      <c r="C39" s="21"/>
       <c r="E39" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C40" s="18"/>
+      <c r="C40" s="21"/>
       <c r="E40" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C41" s="18"/>
+      <c r="C41" s="21"/>
       <c r="E41" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C42" s="18"/>
+      <c r="C42" s="21"/>
       <c r="E42" s="15" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C43" s="18"/>
+      <c r="C43" s="21"/>
       <c r="E43" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C44" s="18"/>
+      <c r="C44" s="21"/>
       <c r="E44" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C45" s="18"/>
+      <c r="C45" s="21"/>
       <c r="E45" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C46" s="18"/>
+      <c r="C46" s="21"/>
       <c r="E46" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C47" s="18"/>
+      <c r="C47" s="21"/>
       <c r="E47" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C48" s="18"/>
+      <c r="C48" s="21"/>
       <c r="E48" s="15" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C49" s="18"/>
+      <c r="C49" s="21"/>
       <c r="E49" s="15" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C50" s="18"/>
+      <c r="C50" s="21"/>
       <c r="E50" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C51" s="18"/>
+      <c r="C51" s="21"/>
       <c r="E51" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C52" s="18"/>
+      <c r="C52" s="21"/>
       <c r="E52" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C53" s="18"/>
+      <c r="C53" s="21"/>
       <c r="E53" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C54" s="18"/>
+      <c r="C54" s="21"/>
       <c r="E54" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C55" s="18"/>
+      <c r="C55" s="21"/>
       <c r="E55" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C56" s="18"/>
+      <c r="C56" s="21"/>
       <c r="E56" s="15" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C57" s="18"/>
+      <c r="C57" s="21"/>
       <c r="E57" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C58" s="18"/>
+      <c r="C58" s="21"/>
       <c r="E58" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C59" s="18"/>
+      <c r="C59" s="21"/>
       <c r="E59" t="s">
         <v>141</v>
       </c>
@@ -2631,7 +2929,7 @@
       <c r="F60" s="9"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="21" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -2639,157 +2937,157 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C62" s="18"/>
+      <c r="C62" s="21"/>
       <c r="E62" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C63" s="18"/>
+      <c r="C63" s="21"/>
       <c r="E63" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C64" s="18"/>
+      <c r="C64" s="21"/>
       <c r="E64" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C65" s="18"/>
+      <c r="C65" s="21"/>
       <c r="E65" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C66" s="18"/>
+      <c r="C66" s="21"/>
       <c r="E66" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C67" s="18"/>
+      <c r="C67" s="21"/>
       <c r="E67" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C68" s="18"/>
+      <c r="C68" s="21"/>
       <c r="E68" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C69" s="18"/>
+      <c r="C69" s="21"/>
       <c r="E69" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C70" s="18"/>
+      <c r="C70" s="21"/>
       <c r="E70" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C71" s="18"/>
+      <c r="C71" s="21"/>
       <c r="E71" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C72" s="18"/>
+      <c r="C72" s="21"/>
       <c r="E72" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C73" s="18"/>
+      <c r="C73" s="21"/>
       <c r="E73" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C74" s="18"/>
+      <c r="C74" s="21"/>
       <c r="E74" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C75" s="18"/>
+      <c r="C75" s="21"/>
       <c r="E75" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C76" s="18"/>
+      <c r="C76" s="21"/>
       <c r="E76" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C77" s="18"/>
+      <c r="C77" s="21"/>
       <c r="E77" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C78" s="18"/>
+      <c r="C78" s="21"/>
       <c r="E78" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C79" s="18"/>
+      <c r="C79" s="21"/>
       <c r="E79" s="15" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C80" s="18"/>
+      <c r="C80" s="21"/>
       <c r="E80" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C81" s="18"/>
+      <c r="C81" s="21"/>
       <c r="E81" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C82" s="18"/>
+      <c r="C82" s="21"/>
       <c r="E82" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C83" s="18"/>
+      <c r="C83" s="21"/>
       <c r="E83" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C84" s="18"/>
+      <c r="C84" s="21"/>
       <c r="E84" s="15" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C85" s="18"/>
+      <c r="C85" s="21"/>
       <c r="E85" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C86" s="18"/>
+      <c r="C86" s="21"/>
       <c r="E86" s="10" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C87" s="18"/>
+      <c r="C87" s="21"/>
       <c r="E87" s="1" t="s">
         <v>110</v>
       </c>
@@ -3346,7 +3644,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97DB269-7E8D-4F8A-91F3-657888A46C31}">
-  <dimension ref="A2:F35"/>
+  <dimension ref="A2:F58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="34.7265625" customWidth="1"/>
@@ -3429,7 +3727,7 @@
         <v>237</v>
       </c>
       <c r="F9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3440,7 +3738,7 @@
         <v>244</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3451,7 +3749,7 @@
         <v>245</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -3462,7 +3760,7 @@
         <v>238</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -3473,7 +3771,7 @@
         <v>246</v>
       </c>
       <c r="F13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -3484,7 +3782,7 @@
         <v>239</v>
       </c>
       <c r="F14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -3493,86 +3791,104 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>156</v>
+      </c>
       <c r="E16" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>156</v>
+      </c>
       <c r="E17" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>156</v>
+      </c>
       <c r="E18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>156</v>
+      </c>
       <c r="E19" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>156</v>
+      </c>
       <c r="E20" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E21" s="15" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>156</v>
+      </c>
       <c r="E22" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E24" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E25" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E27" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E28" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E29" s="15" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E30" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E31" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="4:5" x14ac:dyDescent="0.35">
       <c r="E32" t="s">
         <v>264</v>
       </c>
@@ -3591,12 +3907,156 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
-        <v>266</v>
+        <v>8</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E36" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E37" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E38" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E39" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E40" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E41" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E42" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E43" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E44" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E45" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E46" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E47" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="E48" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E49" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E50" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E51" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E52" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E53" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E54" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E55" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E56" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E57" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E58" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E35" r:id="rId1" display="https://algomaster.io/practice/dsa/binary-search?list=am-600" xr:uid="{15AFAAEB-1B63-45BE-AA37-C033C442B8DE}"/>
+    <hyperlink ref="E36" r:id="rId2" display="https://algomaster.io/practice/dsa/first-bad-version?list=am-600" xr:uid="{3047D248-F347-4E43-BC1B-7FF3B5225555}"/>
+    <hyperlink ref="E37" r:id="rId3" display="https://algomaster.io/practice/dsa/valid-perfect-square?list=am-600" xr:uid="{C31EC209-F498-40B8-BAB7-4AAEA832DE44}"/>
+    <hyperlink ref="E38" r:id="rId4" display="https://algomaster.io/practice/dsa/search-insert-position?list=am-600" xr:uid="{87656A6A-D9E2-4561-B527-9CD4E3853C51}"/>
+    <hyperlink ref="E39" r:id="rId5" display="https://algomaster.io/practice/dsa/guess-number-higher-or-lower?list=am-600" xr:uid="{6CB1BC3F-91C9-4111-84DF-9DB00D1F53CA}"/>
+    <hyperlink ref="E40" r:id="rId6" display="https://algomaster.io/practice/dsa/find-smallest-letter-greater-than-target?list=am-600" xr:uid="{99D800D7-180D-4083-8A42-D7EA5EB98B48}"/>
+    <hyperlink ref="E41" r:id="rId7" display="https://algomaster.io/practice/dsa/find-first-and-last-position-of-element-in-sorted-array?list=am-600" xr:uid="{C37DC84D-A12F-4833-80D8-2ABEA959833B}"/>
+    <hyperlink ref="E42" r:id="rId8" display="https://algomaster.io/practice/dsa/search-in-rotated-sorted-array?list=am-600" xr:uid="{4877EC37-6F23-4BBB-B8A4-4B73C5D265D4}"/>
+    <hyperlink ref="E43" r:id="rId9" display="https://algomaster.io/practice/dsa/search-in-rotated-sorted-array-ii?list=am-600" xr:uid="{999EF086-7B9B-4D80-AB46-9D7D3B5442BE}"/>
+    <hyperlink ref="E44" r:id="rId10" display="https://algomaster.io/practice/dsa/find-peak-element?list=am-600" xr:uid="{BD406BB4-B9E9-4927-8331-DBF19BA17528}"/>
+    <hyperlink ref="E45" r:id="rId11" display="https://algomaster.io/practice/dsa/random-pick-with-weight?list=am-600" xr:uid="{A64896E8-DDA3-4057-BC2A-D6CBEF930C4C}"/>
+    <hyperlink ref="E46" r:id="rId12" display="https://algomaster.io/practice/dsa/find-k-closest-elements?list=am-600" xr:uid="{2269FD94-4245-4332-AA9D-9EAC8347FC3B}"/>
+    <hyperlink ref="E47" r:id="rId13" display="https://algomaster.io/practice/dsa/heaters?list=am-600" xr:uid="{13BD01AB-3AF6-4C0A-8066-F70442ECC3C1}"/>
+    <hyperlink ref="E48" r:id="rId14" display="https://algomaster.io/practice/dsa/koko-eating-bananas?list=am-600" xr:uid="{82D5AE41-29C6-40C4-ADD6-219C45CE6BB3}"/>
+    <hyperlink ref="E49" r:id="rId15" display="https://algomaster.io/practice/dsa/capacity-to-ship-packages-within-d-days?list=am-600" xr:uid="{5153B6C4-2A11-48D6-BBEB-28C1ED0C6939}"/>
+    <hyperlink ref="E50" r:id="rId16" display="https://algomaster.io/practice/dsa/minimum-number-of-days-to-make-m-bouquets?list=am-600" xr:uid="{392B1109-A04C-461E-9955-6EDA6209E5A2}"/>
+    <hyperlink ref="E51" r:id="rId17" display="https://algomaster.io/practice/dsa/find-minimum-in-rotated-sorted-array?list=am-600" xr:uid="{7E4B6C0B-FAFC-4B83-9477-803BC945294B}"/>
+    <hyperlink ref="E52" r:id="rId18" display="https://algomaster.io/practice/dsa/search-a-2d-matrix?list=am-600" xr:uid="{85B315CE-5D64-486D-B21E-722C116F3E86}"/>
+    <hyperlink ref="E53" r:id="rId19" display="https://algomaster.io/practice/dsa/search-a-2d-matrix-ii?list=am-600" xr:uid="{3546510C-41D5-4AE0-AE86-BB43A488169F}"/>
+    <hyperlink ref="E54" r:id="rId20" display="https://algomaster.io/practice/dsa/magnetic-force-between-two-balls?list=am-600" xr:uid="{2A50C54C-E134-4D6D-A0CF-B44BE5BB2732}"/>
+    <hyperlink ref="E55" r:id="rId21" display="https://algomaster.io/practice/dsa/find-in-mountain-array?list=am-600" xr:uid="{BD5816CF-7341-4EBF-B470-EFC7AE4E4B52}"/>
+    <hyperlink ref="E56" r:id="rId22" display="https://algomaster.io/practice/dsa/split-array-largest-sum?list=am-600" xr:uid="{8D8E498B-761B-4A44-8A93-B72E2C4F16C9}"/>
+    <hyperlink ref="E57" r:id="rId23" display="https://algomaster.io/practice/dsa/median-of-two-sorted-arrays?list=am-600" xr:uid="{0AB40610-21F2-4EB7-A3B7-9CE924767F09}"/>
+    <hyperlink ref="E58" r:id="rId24" display="https://algomaster.io/practice/dsa/find-k-th-smallest-pair-distance?list=am-600" xr:uid="{FF66494C-3634-4A2D-8D35-551839546B6B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
 
